--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008432213998538026</v>
       </c>
       <c r="C2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>36065211</v>
+        <v>4178128</v>
       </c>
       <c r="L2" t="n">
-        <v>20004626</v>
+        <v>1895815</v>
       </c>
       <c r="M2" t="n">
-        <v>4900892</v>
+        <v>403273</v>
       </c>
       <c r="N2" t="n">
-        <v>252972</v>
+        <v>7581</v>
       </c>
       <c r="O2" t="n">
-        <v>2927201</v>
+        <v>237492</v>
       </c>
       <c r="P2" t="n">
-        <v>1124174</v>
+        <v>69184</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999873638153076</v>
+        <v>0.9999608993530273</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8723072409629822</v>
+        <v>0.7695975303649902</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7607625126838684</v>
+        <v>0.6007698178291321</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7030479907989502</v>
+        <v>0.4822264909744263</v>
       </c>
       <c r="U2" t="n">
-        <v>0.380682647228241</v>
+        <v>0.07956298440694809</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7429133057594299</v>
+        <v>0.5214183926582336</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8385635018348694</v>
+        <v>0.7079675197601318</v>
       </c>
       <c r="X2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="AG2" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AH2" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AI2" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563227891921997</v>
+        <v>0.9555724859237671</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114070534706116</v>
+        <v>0.9118132591247559</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580120801925659</v>
+        <v>0.8582125902175903</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619145274162292</v>
+        <v>0.6612037420272827</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019697904586792</v>
+        <v>0.9019888043403625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002020802637879015</v>
       </c>
       <c r="C3" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>36065211</v>
+        <v>4178128</v>
       </c>
       <c r="E3" t="n">
-        <v>4249818</v>
+        <v>815618</v>
       </c>
       <c r="F3" t="n">
-        <v>96507</v>
+        <v>29605</v>
       </c>
       <c r="G3" t="n">
-        <v>9453</v>
+        <v>1782</v>
       </c>
       <c r="H3" t="n">
-        <v>6238</v>
+        <v>1775</v>
       </c>
       <c r="I3" t="n">
-        <v>348</v>
+        <v>88</v>
       </c>
       <c r="J3" t="n">
-        <v>80556317</v>
+        <v>10069372</v>
       </c>
       <c r="K3" t="n">
-        <v>85620944</v>
+        <v>10138111</v>
       </c>
       <c r="L3" t="n">
-        <v>98730991</v>
+        <v>11846665</v>
       </c>
       <c r="M3" t="n">
-        <v>121775656</v>
+        <v>15044223</v>
       </c>
       <c r="N3" t="n">
-        <v>130200957</v>
+        <v>16238524</v>
       </c>
       <c r="O3" t="n">
-        <v>126236794</v>
+        <v>15687086</v>
       </c>
       <c r="P3" t="n">
-        <v>129564457</v>
+        <v>16193872</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.892092764377594</v>
+        <v>0.8311309814453125</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7604545950889587</v>
+        <v>0.572839081287384</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6549967527389526</v>
+        <v>0.429572731256485</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3535632193088531</v>
+        <v>0.08444538712501526</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7177605032920837</v>
+        <v>0.4648202359676361</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7266227006912231</v>
+        <v>0.357373833656311</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="Z3" t="n">
-        <v>1591784</v>
+        <v>198388</v>
       </c>
       <c r="AA3" t="n">
-        <v>68580</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>54698</v>
+        <v>6867</v>
       </c>
       <c r="AC3" t="n">
-        <v>326</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80556960</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>89132297</v>
+        <v>11165177</v>
       </c>
       <c r="AG3" t="n">
-        <v>102695121</v>
+        <v>12815311</v>
       </c>
       <c r="AH3" t="n">
-        <v>122784182</v>
+        <v>15344357</v>
       </c>
       <c r="AI3" t="n">
-        <v>130370832</v>
+        <v>16295858</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126850187</v>
+        <v>15855036</v>
       </c>
       <c r="AK3" t="n">
-        <v>129674836</v>
+        <v>16209148</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575629830360413</v>
+        <v>0.9574769735336304</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099209904670715</v>
+        <v>0.9097115993499756</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572890758514404</v>
+        <v>0.8566603064537048</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613048911094666</v>
+        <v>0.6601800322532654</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014734625816345</v>
+        <v>0.9011573195457458</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03191057304788653</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>4943223</v>
+        <v>1155193</v>
       </c>
       <c r="E4" t="n">
-        <v>20004626</v>
+        <v>1895815</v>
       </c>
       <c r="F4" t="n">
-        <v>1177690</v>
+        <v>216552</v>
       </c>
       <c r="G4" t="n">
-        <v>55967</v>
+        <v>11749</v>
       </c>
       <c r="H4" t="n">
-        <v>115637</v>
+        <v>28391</v>
       </c>
       <c r="I4" t="n">
-        <v>8975</v>
+        <v>1797</v>
       </c>
       <c r="J4" t="n">
-        <v>643</v>
+        <v>248</v>
       </c>
       <c r="K4" t="n">
-        <v>5279409</v>
+        <v>1250850</v>
       </c>
       <c r="L4" t="n">
-        <v>6290868</v>
+        <v>1259828</v>
       </c>
       <c r="M4" t="n">
-        <v>2070029</v>
+        <v>433000</v>
       </c>
       <c r="N4" t="n">
-        <v>411550</v>
+        <v>87702</v>
       </c>
       <c r="O4" t="n">
-        <v>1012964</v>
+        <v>217981</v>
       </c>
       <c r="P4" t="n">
-        <v>216421</v>
+        <v>28538</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999936819076538</v>
+        <v>0.9999804496765137</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8820890784263611</v>
+        <v>0.7991815209388733</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7606085538864136</v>
+        <v>0.5864720940589905</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6781722903251648</v>
+        <v>0.4543793201446533</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3666220903396606</v>
+        <v>0.08193150907754898</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7301203012466431</v>
+        <v>0.4914953112602234</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7785900831222534</v>
+        <v>0.4749821722507477</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1650806</v>
+        <v>208961</v>
       </c>
       <c r="Z4" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AA4" t="n">
-        <v>664902</v>
+        <v>83070</v>
       </c>
       <c r="AB4" t="n">
-        <v>44224</v>
+        <v>5580</v>
       </c>
       <c r="AC4" t="n">
-        <v>9155</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1768056</v>
+        <v>223784</v>
       </c>
       <c r="AG4" t="n">
-        <v>2326738</v>
+        <v>291182</v>
       </c>
       <c r="AH4" t="n">
-        <v>1061503</v>
+        <v>132866</v>
       </c>
       <c r="AI4" t="n">
-        <v>241675</v>
+        <v>30368</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399571</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569424390792847</v>
+        <v>0.9565237760543823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663366317749</v>
+        <v>0.9107611775398254</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576504588127136</v>
+        <v>0.8574357628822327</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616095304489136</v>
+        <v>0.660691499710083</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017215967178345</v>
+        <v>0.9015728235244751</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>230087</v>
+        <v>70126</v>
       </c>
       <c r="E5" t="n">
-        <v>1700907</v>
+        <v>353286</v>
       </c>
       <c r="F5" t="n">
-        <v>4900892</v>
+        <v>403273</v>
       </c>
       <c r="G5" t="n">
-        <v>139531</v>
+        <v>23788</v>
       </c>
       <c r="H5" t="n">
-        <v>470600</v>
+        <v>80889</v>
       </c>
       <c r="I5" t="n">
-        <v>40240</v>
+        <v>7389</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4362436</v>
+        <v>848911</v>
       </c>
       <c r="L5" t="n">
-        <v>6301515</v>
+        <v>1413692</v>
       </c>
       <c r="M5" t="n">
-        <v>2581423</v>
+        <v>535504</v>
       </c>
       <c r="N5" t="n">
-        <v>462521</v>
+        <v>82193</v>
       </c>
       <c r="O5" t="n">
-        <v>1151041</v>
+        <v>273441</v>
       </c>
       <c r="P5" t="n">
-        <v>422948</v>
+        <v>124406</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999951124191284</v>
+        <v>0.9999849200248718</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9265819787979126</v>
+        <v>0.8720905780792236</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9041150212287903</v>
+        <v>0.837139368057251</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9645814299583435</v>
+        <v>0.9410024285316467</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9933443665504456</v>
+        <v>0.9896506667137146</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9835221171379089</v>
+        <v>0.9700644612312317</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9951314926147461</v>
+        <v>0.9906832575798035</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64693</v>
+        <v>8176</v>
       </c>
       <c r="Z5" t="n">
-        <v>684803</v>
+        <v>86508</v>
       </c>
       <c r="AA5" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AB5" t="n">
-        <v>79806</v>
+        <v>10008</v>
       </c>
       <c r="AC5" t="n">
-        <v>233442</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1715628</v>
+        <v>213765</v>
       </c>
       <c r="AG5" t="n">
-        <v>2369631</v>
+        <v>298810</v>
       </c>
       <c r="AH5" t="n">
-        <v>1067808</v>
+        <v>134564</v>
       </c>
       <c r="AI5" t="n">
-        <v>242334</v>
+        <v>30507</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401815</v>
+        <v>50502</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734734296798706</v>
+        <v>0.9733461737632751</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642394185066223</v>
+        <v>0.9640599489212036</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837862849235535</v>
+        <v>0.9837091565132141</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996314525604248</v>
+        <v>0.9962917566299438</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938978552818298</v>
+        <v>0.9938759207725525</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998382568359375</v>
+        <v>0.9983792304992676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>155</v>
+        <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>94359</v>
+        <v>19407</v>
       </c>
       <c r="E6" t="n">
-        <v>139177</v>
+        <v>22949</v>
       </c>
       <c r="F6" t="n">
-        <v>153356</v>
+        <v>29415</v>
       </c>
       <c r="G6" t="n">
-        <v>252972</v>
+        <v>7581</v>
       </c>
       <c r="H6" t="n">
-        <v>68363</v>
+        <v>9481</v>
       </c>
       <c r="I6" t="n">
-        <v>7111</v>
+        <v>899</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>52110</v>
+        <v>6591</v>
       </c>
       <c r="Z6" t="n">
-        <v>43017</v>
+        <v>5395</v>
       </c>
       <c r="AA6" t="n">
-        <v>87434</v>
+        <v>11026</v>
       </c>
       <c r="AB6" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AC6" t="n">
-        <v>55925</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>11346</v>
+        <v>5991</v>
       </c>
       <c r="E7" t="n">
-        <v>186535</v>
+        <v>62019</v>
       </c>
       <c r="F7" t="n">
-        <v>604491</v>
+        <v>142942</v>
       </c>
       <c r="G7" t="n">
-        <v>188863</v>
+        <v>44104</v>
       </c>
       <c r="H7" t="n">
-        <v>2927201</v>
+        <v>237492</v>
       </c>
       <c r="I7" t="n">
-        <v>159747</v>
+        <v>18365</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>6486</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237939</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60821</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>133</v>
       </c>
       <c r="E8" t="n">
-        <v>14431</v>
+        <v>5956</v>
       </c>
       <c r="F8" t="n">
-        <v>37985</v>
+        <v>14486</v>
       </c>
       <c r="G8" t="n">
-        <v>17736</v>
+        <v>6279</v>
       </c>
       <c r="H8" t="n">
-        <v>352126</v>
+        <v>97445</v>
       </c>
       <c r="I8" t="n">
-        <v>1124174</v>
+        <v>69184</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
